--- a/output/Job_Applications_Tracker_2026-05.xlsx
+++ b/output/Job_Applications_Tracker_2026-05.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,23 +430,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
@@ -550,86 +544,6 @@
           <t>Response Received</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Engineering Intern</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Curtiss-Wright Corporation</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Technology / Semiconductor</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Portland, OR, Newtown, PA</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>https://curtisswright.wd1.myworkdayjobs.com/cw_external_career_site/job/US-OR-Portland-Williams/Intern----Engineering_JR11326?utm_source=Simplify&amp;ref=Simplify</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.curtiss-wrightcorporation.com</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>SimplifyJobs/GitHub</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Strong technical overlap with FPGA/embedded roles but limited semiconductor/photonics research alignment and poor location fit for internship.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Your_Name_Resume_Curtiss-Wright_Corporation_Engineering_Intern.tex</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Manual Required</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -646,12 +560,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -676,7 +590,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -696,7 +610,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +631,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
